--- a/backtest_runs/20260410_193731/by_symbol/FZCM/FZCM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FZCM/FZCM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>101403.68</v>
@@ -679,7 +679,7 @@
         <v>-2693.280000000003</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>98710.40000000001</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>98710.40000000001</v>
@@ -863,7 +863,7 @@
         <v>-1205.280000000003</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>97505.12</v>
@@ -909,7 +909,7 @@
         <v>-2197.280000000003</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>95307.84</v>
@@ -1231,7 +1231,7 @@
         <v>-3263.679999999992</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>94246.40000000001</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>94246.40000000001</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>97177.75999999999</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>99107.20000000001</v>
